--- a/artfynd/A 24923-2022 artfynd.xlsx
+++ b/artfynd/A 24923-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24923-2022 artfynd.xlsx
+++ b/artfynd/A 24923-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>104158313</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>875934.5595955034</v>
+        <v>875935</v>
       </c>
       <c r="R2" t="n">
-        <v>7345805.061714797</v>
+        <v>7345805</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-06-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -795,16 +780,11 @@
         <v>104158274</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>876014.4404010461</v>
+        <v>876014</v>
       </c>
       <c r="R3" t="n">
-        <v>7345734.249378229</v>
+        <v>7345734</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +845,9 @@
           <t>2022-06-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
